--- a/RSI Modular - copia/tabla_maestra_GSPC.xlsx
+++ b/RSI Modular - copia/tabla_maestra_GSPC.xlsx
@@ -557,7 +557,7 @@
         <v>-0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.52</v>
+        <v>-0.57</v>
       </c>
       <c r="I3" t="n">
         <v>-2.38</v>
@@ -607,7 +607,7 @@
         <v>4.47</v>
       </c>
       <c r="K4" t="n">
-        <v>5.95</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="5">
@@ -627,28 +627,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>-0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
       <c r="H5" t="n">
         <v>-0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.91</v>
+        <v>-0.86</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.83</v>
+        <v>-1.74</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.97</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="6">
@@ -769,7 +769,7 @@
         <v>-0.26</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="G9" t="n">
         <v>-0.42</v>
@@ -778,7 +778,7 @@
         <v>-0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.17</v>
+        <v>-1.4</v>
       </c>
       <c r="J9" t="n">
         <v>-2.94</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F11" t="n">
         <v>0.22</v>
@@ -843,7 +843,7 @@
         <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="I11" t="n">
         <v>-2.27</v>
@@ -1050,7 +1050,7 @@
         <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" t="n">
         <v>13.6</v>
@@ -1100,7 +1100,7 @@
         <v>75</v>
       </c>
       <c r="K4" t="n">
-        <v>67.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1120,28 +1120,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>34.8</v>
+        <v>35.4</v>
       </c>
       <c r="F5" t="n">
         <v>41.5</v>
       </c>
       <c r="G5" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="H5" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="I5" t="n">
-        <v>41.3</v>
+        <v>41.9</v>
       </c>
       <c r="J5" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="K5" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="6">
@@ -1262,7 +1262,7 @@
         <v>24.2</v>
       </c>
       <c r="F9" t="n">
-        <v>37.5</v>
+        <v>36.4</v>
       </c>
       <c r="G9" t="n">
         <v>28.1</v>
@@ -1271,7 +1271,7 @@
         <v>21.9</v>
       </c>
       <c r="I9" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="J9" t="n">
         <v>25.9</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>47.4</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>68.40000000000001</v>
@@ -1336,7 +1336,7 @@
         <v>57.9</v>
       </c>
       <c r="H11" t="n">
-        <v>16.7</v>
+        <v>15.8</v>
       </c>
       <c r="I11" t="n">
         <v>12.5</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
